--- a/elite-data/manifest-templates/EL_template_GenotypingHumanTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_GenotypingHumanTemplate.xlsx
@@ -362,7 +362,7 @@
     <t>C</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>TRUE</t>
@@ -377,7 +377,7 @@
     <t>F</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>AU/ml</t>
@@ -413,7 +413,7 @@
     <t>g/l</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>gm</t>
